--- a/output/StructureDefinition-mh-toc-parity.xlsx
+++ b/output/StructureDefinition-mh-toc-parity.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2035" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2034" uniqueCount="454">
   <si>
     <t>Property</t>
   </si>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Observation</t>
+    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-simple-observation</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -272,10 +272,7 @@
     <t>assessment observation</t>
   </si>
   <si>
-    <t>Measurements and simple assertions made about a patient, device or other subject.</t>
-  </si>
-  <si>
-    <t>Used for simple observations such as device measurements, laboratory atomic results, vital signs, height, weight, smoking status, comments, etc.  Other resources are used to provide context for observations such as laboratory reports, etc.</t>
+    <t>\-</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
@@ -570,7 +567,7 @@
     <t>Observation.status</t>
   </si>
   <si>
-    <t>registered | preliminary | final | amended +</t>
+    <t>(USCDI) registered | preliminary | final | amended +</t>
   </si>
   <si>
     <t>The status of the result value.</t>
@@ -613,7 +610,7 @@
 </t>
   </si>
   <si>
-    <t>Classification of  type of observation</t>
+    <t>(USCDI) Classification of  type of observation</t>
   </si>
   <si>
     <t>A code that classifies the general type of observation being made.</t>
@@ -625,35 +622,35 @@
     <t>Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
-    <t>FHIR and US Core codes for high level observation categories.</t>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:us-core</t>
+  </si>
+  <si>
+    <t>us-core</t>
+  </si>
+  <si>
+    <t>Note that other codes are permitted, see [Required Bindings When Slicing by Value Sets](http://hl7.org/fhir/us/core/general-requirements.html#required-bindings-when-slicing-by-valuesets)</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-simple-observation-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:$this}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:us-core</t>
-  </si>
-  <si>
-    <t>us-core</t>
-  </si>
-  <si>
-    <t>𝗔𝗗𝗗𝗜𝗧𝗜𝗢𝗡𝗔𝗟 𝗨𝗦𝗖𝗗𝗜: US Core classification of type of observation</t>
-  </si>
-  <si>
-    <t>Note that other codes are permitted, see [Required Bindings When Slicing by Value Sets](general-requirements.html#required-bindings-when-slicing-by-valuesets)</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -683,12 +680,6 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes identifying names of simple observations.</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
@@ -713,11 +704,11 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|Group|Device|http://hl7.org/fhir/us/core/StructureDefinition/us-core-location)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
 </t>
   </si>
   <si>
-    <t>Who and/or what the observation is about</t>
+    <t>(USCDI) Who and/or what the observation is about</t>
   </si>
   <si>
     <t>The patient, or group of patients, location, or device this observation is about and into whose record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
@@ -806,10 +797,10 @@
 PeriodTiminginstant</t>
   </si>
   <si>
-    <t>Clinically relevant time/time-period for observation</t>
-  </si>
-  <si>
-    <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g., human patients - this is usually called the "physiologically relevant time".</t>
+    <t>(USCDI) Clinically relevant time/time-period for observation</t>
+  </si>
+  <si>
+    <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time".</t>
   </si>
   <si>
     <t>At least a date should be present unless this observation is a historical report.</t>
@@ -858,11 +849,11 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization|PractitionerRole|http://hl7.org/fhir/us/core/StructureDefinition/us-core-careteam|http://hl7.org/fhir/us/core/StructureDefinition/us-core-relatedperson)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization|http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|PractitionerRole|http://hl7.org/fhir/us/core/StructureDefinition/us-core-careteam|http://hl7.org/fhir/us/core/StructureDefinition/us-core-relatedperson)
 </t>
   </si>
   <si>
-    <t>Who is responsible for the observation</t>
+    <t>(USCDI) Who is responsible for the observation</t>
   </si>
   <si>
     <t>Who was responsible for asserting the observed value as "true".</t>
@@ -890,7 +881,7 @@
 timedateTimePeriod</t>
   </si>
   <si>
-    <t>Actual result</t>
+    <t>(USCDI) Actual result</t>
   </si>
   <si>
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
@@ -1023,6 +1014,9 @@
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>Codes describing anatomical locations. May include laterality.</t>
@@ -1345,14 +1339,14 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|http://hl7.org/fhir/us/core/StructureDefinition/us-core-documentreference|http://hl7.org/fhir/us/core/StructureDefinition/us-core-questionnaireresponse|ImagingStudy|Media|MolecularSequence)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation)
 </t>
   </si>
   <si>
-    <t>𝗔𝗗𝗗𝗜𝗧𝗜𝗢𝗡𝗔𝗟 𝗨𝗦𝗖𝗗𝗜: US Core Profiles or other resource the observation is made from</t>
-  </si>
-  <si>
-    <t>US Core Observations, DocumentReference, QuestionnaireResponse or other resource from which this observation value is derived.</t>
+    <t>(USCDI) US Core Profiles or other resource the observation is made from</t>
+  </si>
+  <si>
+    <t>Observations or or other resource such as a QuestionnaireResponse from which this observation value is derived.</t>
   </si>
   <si>
     <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
@@ -1401,6 +1395,9 @@
   </si>
   <si>
     <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
+  </si>
+  <si>
+    <t>Codes identifying names of simple observations.</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -1789,7 +1786,7 @@
     <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="126.94140625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="148.8828125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="59.63671875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
@@ -1973,7 +1970,7 @@
         <v>84</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -2035,19 +2032,19 @@
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AK2" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="AK2" t="s" s="2">
+      <c r="AL2" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AM2" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>20</v>
@@ -2058,10 +2055,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2072,28 +2069,28 @@
         <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2143,13 +2140,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -2178,10 +2175,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2192,25 +2189,25 @@
         <v>80</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2261,19 +2258,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>103</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>104</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -2296,10 +2293,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2310,28 +2307,28 @@
         <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>109</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2381,19 +2378,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2416,10 +2413,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2430,7 +2427,7 @@
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2442,16 +2439,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2477,43 +2474,43 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>119</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2536,21 +2533,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2562,16 +2559,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>124</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>125</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2621,31 +2618,31 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN7" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>127</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>20</v>
@@ -2656,14 +2653,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2682,16 +2679,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>133</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2741,7 +2738,7 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -2765,7 +2762,7 @@
         <v>20</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>20</v>
@@ -2776,14 +2773,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2802,16 +2799,16 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>141</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2861,7 +2858,7 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -2873,7 +2870,7 @@
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -2885,7 +2882,7 @@
         <v>20</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>20</v>
@@ -2896,14 +2893,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2916,25 +2913,25 @@
         <v>20</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>20</v>
@@ -2983,7 +2980,7 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -2995,7 +2992,7 @@
         <v>20</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -3007,7 +3004,7 @@
         <v>20</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>20</v>
@@ -3018,10 +3015,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3041,20 +3038,20 @@
         <v>20</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="M11" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -3103,7 +3100,7 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3115,22 +3112,22 @@
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>20</v>
@@ -3138,14 +3135,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3161,20 +3158,20 @@
         <v>20</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -3223,7 +3220,7 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3235,19 +3232,19 @@
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="AL12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>20</v>
@@ -3258,14 +3255,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3281,19 +3278,19 @@
         <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3343,7 +3340,7 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3355,19 +3352,19 @@
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="AL13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>20</v>
@@ -3378,10 +3375,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3389,34 +3386,34 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H14" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G14" t="s" s="2">
+      <c r="I14" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H14" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="J14" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="N14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -3441,58 +3438,58 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="Y14" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="Z14" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="Z14" t="s" s="2">
+      <c r="AA14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK14" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AA14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK14" t="s" s="2">
+      <c r="AL14" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>20</v>
@@ -3500,10 +3497,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3511,13 +3508,13 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>20</v>
@@ -3526,19 +3523,19 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
@@ -3563,29 +3560,29 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB15" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3597,7 +3594,7 @@
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>20</v>
@@ -3609,10 +3606,10 @@
         <v>20</v>
       </c>
       <c r="AN15" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>20</v>
@@ -3620,13 +3617,13 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="C16" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>20</v>
@@ -3639,7 +3636,7 @@
         <v>81</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>20</v>
@@ -3648,19 +3645,19 @@
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="L16" t="s" s="2">
-        <v>203</v>
-      </c>
       <c r="M16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3685,13 +3682,13 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -3709,7 +3706,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3721,7 +3718,7 @@
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>20</v>
@@ -3733,10 +3730,10 @@
         <v>20</v>
       </c>
       <c r="AN16" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>20</v>
@@ -3744,45 +3741,45 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H17" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G17" t="s" s="2">
+      <c r="I17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J17" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H17" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K17" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -3792,84 +3789,82 @@
         <v>20</v>
       </c>
       <c r="S17" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="Y17" s="2"/>
+      <c r="Z17" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="T17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X17" t="s" s="2">
+      <c r="AA17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK17" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="AL17" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="Z17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AA17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>220</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3877,34 +3872,34 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H18" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G18" t="s" s="2">
+      <c r="I18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J18" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H18" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J18" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K18" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -3953,34 +3948,34 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>20</v>
@@ -3988,10 +3983,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4011,19 +4006,19 @@
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4073,7 +4068,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4085,7 +4080,7 @@
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>20</v>
@@ -4094,13 +4089,13 @@
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>20</v>
@@ -4108,45 +4103,45 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K20" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -4195,34 +4190,34 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>20</v>
@@ -4230,45 +4225,45 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H21" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H21" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="I21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -4317,34 +4312,34 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>20</v>
@@ -4352,10 +4347,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4366,28 +4361,28 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J22" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K22" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4437,19 +4432,19 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>20</v>
@@ -4458,13 +4453,13 @@
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>20</v>
@@ -4472,10 +4467,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4489,26 +4484,26 @@
         <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4557,7 +4552,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4569,22 +4564,22 @@
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>20</v>
@@ -4592,10 +4587,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4606,31 +4601,31 @@
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H24" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="I24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4679,45 +4674,45 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI24" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AJ24" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP24" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>286</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4728,7 +4723,7 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -4740,19 +4735,19 @@
         <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="O25" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4777,55 +4772,55 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI25" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="Y25" t="s" s="2">
+      <c r="AJ25" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>20</v>
@@ -4836,14 +4831,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4862,19 +4857,19 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="O26" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4899,13 +4894,13 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -4923,7 +4918,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4935,33 +4930,33 @@
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AO26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP26" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>308</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4984,19 +4979,19 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5045,7 +5040,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5057,7 +5052,7 @@
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>20</v>
@@ -5066,10 +5061,10 @@
         <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
@@ -5080,10 +5075,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5094,7 +5089,7 @@
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -5106,16 +5101,16 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5141,69 +5136,69 @@
         <v>20</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="Z28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="AA28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>326</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5214,7 +5209,7 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -5226,19 +5221,19 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5263,55 +5258,55 @@
         <v>20</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="Y29" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="Z29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -5322,10 +5317,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5336,7 +5331,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5348,16 +5343,16 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5407,45 +5402,45 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>344</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5456,7 +5451,7 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -5468,16 +5463,16 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5527,45 +5522,45 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP31" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>353</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5588,19 +5583,19 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5649,7 +5644,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5661,19 +5656,19 @@
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -5684,10 +5679,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5698,7 +5693,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5710,13 +5705,13 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5767,13 +5762,13 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
@@ -5791,7 +5786,7 @@
         <v>20</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>20</v>
@@ -5802,14 +5797,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5828,16 +5823,16 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="L34" t="s" s="2">
-        <v>139</v>
-      </c>
       <c r="M34" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5887,7 +5882,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5899,7 +5894,7 @@
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
@@ -5911,7 +5906,7 @@
         <v>20</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
@@ -5922,14 +5917,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5942,25 +5937,25 @@
         <v>20</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -6009,7 +6004,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6021,7 +6016,7 @@
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>20</v>
@@ -6033,7 +6028,7 @@
         <v>20</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
@@ -6044,10 +6039,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6058,7 +6053,7 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -6070,13 +6065,13 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6127,31 +6122,31 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -6162,10 +6157,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6176,7 +6171,7 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -6188,13 +6183,13 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6245,19 +6240,19 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
@@ -6266,10 +6261,10 @@
         <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
@@ -6280,10 +6275,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6294,7 +6289,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -6306,19 +6301,19 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6343,55 +6338,55 @@
         <v>20</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="Z38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="AA38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>396</v>
-      </c>
       <c r="AN38" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
@@ -6402,10 +6397,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6428,19 +6423,19 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6465,13 +6460,13 @@
         <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -6489,7 +6484,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6501,19 +6496,19 @@
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
@@ -6524,10 +6519,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6538,7 +6533,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6550,17 +6545,17 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -6609,19 +6604,19 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>20</v>
@@ -6633,7 +6628,7 @@
         <v>20</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>20</v>
@@ -6644,10 +6639,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6658,7 +6653,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6670,13 +6665,13 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6727,19 +6722,19 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
@@ -6748,10 +6743,10 @@
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
@@ -6762,10 +6757,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6785,19 +6780,19 @@
         <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6847,7 +6842,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6859,7 +6854,7 @@
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>20</v>
@@ -6868,10 +6863,10 @@
         <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
@@ -6882,10 +6877,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6899,25 +6894,25 @@
         <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6967,7 +6962,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6979,7 +6974,7 @@
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
@@ -6988,10 +6983,10 @@
         <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>20</v>
@@ -7002,10 +6997,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7025,22 +7020,22 @@
         <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7089,7 +7084,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7101,7 +7096,7 @@
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
@@ -7110,10 +7105,10 @@
         <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>20</v>
@@ -7124,10 +7119,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7138,7 +7133,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -7150,13 +7145,13 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7207,13 +7202,13 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
@@ -7231,7 +7226,7 @@
         <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -7242,14 +7237,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7268,16 +7263,16 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="L46" t="s" s="2">
-        <v>139</v>
-      </c>
       <c r="M46" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7327,7 +7322,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7339,7 +7334,7 @@
         <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
@@ -7351,7 +7346,7 @@
         <v>20</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>20</v>
@@ -7362,14 +7357,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7382,25 +7377,25 @@
         <v>20</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7449,7 +7444,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7461,7 +7456,7 @@
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
@@ -7473,7 +7468,7 @@
         <v>20</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
@@ -7484,10 +7479,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7495,34 +7490,34 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J48" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="G48" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K48" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M48" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>440</v>
-      </c>
       <c r="O48" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7547,58 +7542,58 @@
         <v>20</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>213</v>
+        <v>439</v>
       </c>
       <c r="Z48" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AA48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>217</v>
-      </c>
       <c r="AN48" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>20</v>
@@ -7606,10 +7601,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7620,31 +7615,31 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J49" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="H49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="K49" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>445</v>
-      </c>
       <c r="O49" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7693,45 +7688,45 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7742,7 +7737,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -7754,19 +7749,19 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="N50" t="s" s="2">
-        <v>450</v>
-      </c>
       <c r="O50" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -7791,55 +7786,55 @@
         <v>20</v>
       </c>
       <c r="X50" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI50" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="Y50" t="s" s="2">
+      <c r="AJ50" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>20</v>
@@ -7850,14 +7845,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7876,19 +7871,19 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="O51" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -7913,13 +7908,13 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -7937,7 +7932,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7949,33 +7944,33 @@
         <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>308</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8001,16 +7996,16 @@
         <v>82</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>454</v>
-      </c>
       <c r="N52" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -8059,7 +8054,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8071,7 +8066,7 @@
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
@@ -8080,10 +8075,10 @@
         <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>

--- a/output/StructureDefinition-mh-toc-parity.xlsx
+++ b/output/StructureDefinition-mh-toc-parity.xlsx
@@ -1346,7 +1346,7 @@
     <t>(USCDI) US Core Profiles or other resource the observation is made from</t>
   </si>
   <si>
-    <t>Observations or or other resource such as a QuestionnaireResponse from which this observation value is derived.</t>
+    <t>Observations from which this observation value is derived.</t>
   </si>
   <si>
     <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>

--- a/output/StructureDefinition-mh-toc-parity.xlsx
+++ b/output/StructureDefinition-mh-toc-parity.xlsx
@@ -4598,7 +4598,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>91</v>
